--- a/hasil/Non-CLAHE/Run8/history.xlsx
+++ b/hasil/Non-CLAHE/Run8/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,16 +460,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5904762148857117</v>
+        <v>0.5095238089561462</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7111111283302307</v>
+        <v>0.4666666686534882</v>
       </c>
       <c r="D2" t="n">
-        <v>0.998525857925415</v>
+        <v>1.139097213745117</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8081330060958862</v>
+        <v>1.102632284164429</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8523809313774109</v>
+        <v>0.8142856955528259</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6888889074325562</v>
+        <v>0.4666666686534882</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4152465164661407</v>
+        <v>0.4391413331031799</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7534125447273254</v>
+        <v>1.204918026924133</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9333333373069763</v>
+        <v>0.8714285492897034</v>
       </c>
       <c r="C4" t="n">
-        <v>0.644444465637207</v>
+        <v>0.5111111402511597</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2228315472602844</v>
+        <v>0.3168623745441437</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7818390727043152</v>
+        <v>1.24668550491333</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>0.9428571462631226</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6888889074325562</v>
+        <v>0.5333333611488342</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1864475607872009</v>
+        <v>0.2077581137418747</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7395357489585876</v>
+        <v>1.18128490447998</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9809523820877075</v>
+        <v>0.9714285731315613</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7333333492279053</v>
+        <v>0.6222222447395325</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1018538698554039</v>
+        <v>0.1465531140565872</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6475421190261841</v>
+        <v>1.034411072731018</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>0.9809523820877075</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7777777910232544</v>
+        <v>0.6888889074325562</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09693269431591034</v>
+        <v>0.1057487279176712</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5663301944732666</v>
+        <v>0.9338509440422058</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.9857142567634583</v>
       </c>
       <c r="C8" t="n">
-        <v>0.800000011920929</v>
+        <v>0.7555555701255798</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08256179094314575</v>
+        <v>0.09561613202095032</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5117948651313782</v>
+        <v>0.8498331904411316</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0.9952380657196045</v>
       </c>
       <c r="C9" t="n">
-        <v>0.800000011920929</v>
+        <v>0.7555555701255798</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03820234164595604</v>
+        <v>0.06541032344102859</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5042259097099304</v>
+        <v>0.7872385382652283</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0.9952380657196045</v>
       </c>
       <c r="C10" t="n">
-        <v>0.800000011920929</v>
+        <v>0.7555555701255798</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03459354862570763</v>
+        <v>0.06054329127073288</v>
       </c>
       <c r="E10" t="n">
-        <v>0.475072056055069</v>
+        <v>0.7427627444267273</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.800000011920929</v>
+        <v>0.7555555701255798</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02108947746455669</v>
+        <v>0.04310453683137894</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4559069275856018</v>
+        <v>0.6956609487533569</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8222222328186035</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02013137750327587</v>
+        <v>0.04114335402846336</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4297062754631042</v>
+        <v>0.6587217450141907</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8222222328186035</v>
+        <v>0.7777777910232544</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02262395061552525</v>
+        <v>0.03530300781130791</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4248484373092651</v>
+        <v>0.622623085975647</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8222222328186035</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02931964956223965</v>
+        <v>0.02595070376992226</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4148075878620148</v>
+        <v>0.5751045942306519</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8222222328186035</v>
+        <v>0.8444444537162781</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01507635321468115</v>
+        <v>0.0255679078400135</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4059602022171021</v>
+        <v>0.5452107787132263</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8222222328186035</v>
+        <v>0.8444444537162781</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0113263800740242</v>
+        <v>0.02031300403177738</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3967317044734955</v>
+        <v>0.5205869078636169</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8222222328186035</v>
+        <v>0.8444444537162781</v>
       </c>
       <c r="D17" t="n">
-        <v>0.009767877869307995</v>
+        <v>0.01844177767634392</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3910425901412964</v>
+        <v>0.5045956373214722</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8222222328186035</v>
+        <v>0.8444444537162781</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00706423120573163</v>
+        <v>0.01346657704561949</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3807420134544373</v>
+        <v>0.4888308942317963</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8222222328186035</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="D19" t="n">
-        <v>0.013994668610394</v>
+        <v>0.01237097941339016</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3663474917411804</v>
+        <v>0.4725349545478821</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8222222328186035</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="D20" t="n">
-        <v>0.007641628850251436</v>
+        <v>0.01005357597023249</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3600771725177765</v>
+        <v>0.457199901342392</v>
       </c>
     </row>
     <row r="21">
@@ -789,10 +789,10 @@
         <v>0.8666666746139526</v>
       </c>
       <c r="D21" t="n">
-        <v>0.008149375207722187</v>
+        <v>0.01123944204300642</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3405797779560089</v>
+        <v>0.4431063234806061</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8222222328186035</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="D22" t="n">
-        <v>0.008636301383376122</v>
+        <v>0.01211360096931458</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3369251191616058</v>
+        <v>0.4276344180107117</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8444444537162781</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00648193946108222</v>
+        <v>0.00970458984375</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3275910615921021</v>
+        <v>0.4099264740943909</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8444444537162781</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="D24" t="n">
-        <v>0.004939955193549395</v>
+        <v>0.008239873684942722</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3122723996639252</v>
+        <v>0.3875597715377808</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8888888955116272</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01292905956506729</v>
+        <v>0.008920738473534584</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3007151782512665</v>
+        <v>0.3661619424819946</v>
       </c>
     </row>
     <row r="26">
@@ -874,10 +874,10 @@
         <v>0.8666666746139526</v>
       </c>
       <c r="D26" t="n">
-        <v>0.006441536359488964</v>
+        <v>0.007711721584200859</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2952715456485748</v>
+        <v>0.3470108509063721</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8666666746139526</v>
+        <v>0.9111111164093018</v>
       </c>
       <c r="D27" t="n">
-        <v>0.008432886563241482</v>
+        <v>0.006062443368136883</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2889783084392548</v>
+        <v>0.3338219821453094</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8444444537162781</v>
+        <v>0.9111111164093018</v>
       </c>
       <c r="D28" t="n">
-        <v>0.004216005094349384</v>
+        <v>0.006704325787723064</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2860212922096252</v>
+        <v>0.3258492946624756</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8888888955116272</v>
+        <v>0.9111111164093018</v>
       </c>
       <c r="D29" t="n">
-        <v>0.003804465057328343</v>
+        <v>0.005444170907139778</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2778904139995575</v>
+        <v>0.3190996050834656</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8888888955116272</v>
+        <v>0.9111111164093018</v>
       </c>
       <c r="D30" t="n">
-        <v>0.003310473170131445</v>
+        <v>0.005316890776157379</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2739216387271881</v>
+        <v>0.3115487694740295</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8888888955116272</v>
+        <v>0.9111111164093018</v>
       </c>
       <c r="D31" t="n">
-        <v>0.002617841586470604</v>
+        <v>0.005792852956801653</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2703870236873627</v>
+        <v>0.3076475858688354</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8888888955116272</v>
+        <v>0.9111111164093018</v>
       </c>
       <c r="D32" t="n">
-        <v>0.004692062735557556</v>
+        <v>0.005029904190450907</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2779521644115448</v>
+        <v>0.3039984703063965</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8888888955116272</v>
+        <v>0.9111111164093018</v>
       </c>
       <c r="D33" t="n">
-        <v>0.004019103012979031</v>
+        <v>0.005685731302946806</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2835158407688141</v>
+        <v>0.3055047690868378</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8888888955116272</v>
+        <v>0.9333333373069763</v>
       </c>
       <c r="D34" t="n">
-        <v>0.003101156326010823</v>
+        <v>0.006770219188183546</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2799782156944275</v>
+        <v>0.3088167905807495</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8888888955116272</v>
+        <v>0.9333333373069763</v>
       </c>
       <c r="D35" t="n">
-        <v>0.002671276684850454</v>
+        <v>0.006421656347811222</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2749694883823395</v>
+        <v>0.3218224346637726</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,30 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8888888955116272</v>
+        <v>0.9111111164093018</v>
       </c>
       <c r="D36" t="n">
-        <v>0.003273195587098598</v>
+        <v>0.003917567431926727</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2719281613826752</v>
+        <v>0.3329276144504547</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.9111111164093018</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.007007554639130831</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.3382514417171478</v>
       </c>
     </row>
   </sheetData>

--- a/hasil/Non-CLAHE/Run8/history.xlsx
+++ b/hasil/Non-CLAHE/Run8/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,16 +460,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5095238089561462</v>
+        <v>0.6000000238418579</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4666666686534882</v>
+        <v>0.7333333492279053</v>
       </c>
       <c r="D2" t="n">
-        <v>1.139097213745117</v>
+        <v>1.021335601806641</v>
       </c>
       <c r="E2" t="n">
-        <v>1.102632284164429</v>
+        <v>0.7604875564575195</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8142856955528259</v>
+        <v>0.8571428656578064</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4666666686534882</v>
+        <v>0.644444465637207</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4391413331031799</v>
+        <v>0.3995943069458008</v>
       </c>
       <c r="E3" t="n">
-        <v>1.204918026924133</v>
+        <v>0.7700668573379517</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8714285492897034</v>
+        <v>0.9047619104385376</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5111111402511597</v>
+        <v>0.7111111283302307</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3168623745441437</v>
+        <v>0.2460674494504929</v>
       </c>
       <c r="E4" t="n">
-        <v>1.24668550491333</v>
+        <v>0.6739279627799988</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9428571462631226</v>
+        <v>0.9666666388511658</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5333333611488342</v>
+        <v>0.6888889074325562</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2077581137418747</v>
+        <v>0.1500607430934906</v>
       </c>
       <c r="E5" t="n">
-        <v>1.18128490447998</v>
+        <v>0.6546729803085327</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>0.9714285731315613</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6222222447395325</v>
+        <v>0.7333333492279053</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1465531140565872</v>
+        <v>0.1035595908761024</v>
       </c>
       <c r="E6" t="n">
-        <v>1.034411072731018</v>
+        <v>0.6085805892944336</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9809523820877075</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6888889074325562</v>
+        <v>0.7555555701255798</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1057487279176712</v>
+        <v>0.06931087374687195</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9338509440422058</v>
+        <v>0.5465577840805054</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9857142567634583</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7555555701255798</v>
+        <v>0.7777777910232544</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09561613202095032</v>
+        <v>0.04558301717042923</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8498331904411316</v>
+        <v>0.5230928063392639</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9952380657196045</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7555555701255798</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06541032344102859</v>
+        <v>0.05144323036074638</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7872385382652283</v>
+        <v>0.4982298612594604</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9952380657196045</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7555555701255798</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06054329127073288</v>
+        <v>0.03146690502762794</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7427627444267273</v>
+        <v>0.4760980308055878</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7555555701255798</v>
+        <v>0.8222222328186035</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04310453683137894</v>
+        <v>0.02892417274415493</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6956609487533569</v>
+        <v>0.4615753591060638</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.800000011920929</v>
+        <v>0.8222222328186035</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04114335402846336</v>
+        <v>0.03625984862446785</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6587217450141907</v>
+        <v>0.4653210937976837</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7777777910232544</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03530300781130791</v>
+        <v>0.0261843204498291</v>
       </c>
       <c r="E13" t="n">
-        <v>0.622623085975647</v>
+        <v>0.4833952188491821</v>
       </c>
     </row>
     <row r="14">
@@ -670,10 +670,10 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02595070376992226</v>
+        <v>0.02076155506074429</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5751045942306519</v>
+        <v>0.4829029440879822</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8444444537162781</v>
+        <v>0.8222222328186035</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0255679078400135</v>
+        <v>0.01826498843729496</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5452107787132263</v>
+        <v>0.4408630430698395</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8444444537162781</v>
+        <v>0.8222222328186035</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02031300403177738</v>
+        <v>0.01233128551393747</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5205869078636169</v>
+        <v>0.4173159301280975</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8444444537162781</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01844177767634392</v>
+        <v>0.01201549917459488</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5045956373214722</v>
+        <v>0.387180507183075</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8444444537162781</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01346657704561949</v>
+        <v>0.0115195270627737</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4888308942317963</v>
+        <v>0.3757595121860504</v>
       </c>
     </row>
     <row r="19">
@@ -755,10 +755,10 @@
         <v>0.8666666746139526</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01237097941339016</v>
+        <v>0.009280392900109291</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4725349545478821</v>
+        <v>0.367584615945816</v>
       </c>
     </row>
     <row r="20">
@@ -772,10 +772,10 @@
         <v>0.8666666746139526</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01005357597023249</v>
+        <v>0.01226649060845375</v>
       </c>
       <c r="E20" t="n">
-        <v>0.457199901342392</v>
+        <v>0.3571659028530121</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8666666746139526</v>
+        <v>0.8888888955116272</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01123944204300642</v>
+        <v>0.009713919833302498</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4431063234806061</v>
+        <v>0.350174218416214</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8666666746139526</v>
+        <v>0.8888888955116272</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01211360096931458</v>
+        <v>0.006020159926265478</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4276344180107117</v>
+        <v>0.3394229710102081</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8666666746139526</v>
+        <v>0.9111111164093018</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00970458984375</v>
+        <v>0.008388317190110683</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4099264740943909</v>
+        <v>0.3370208144187927</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8666666746139526</v>
+        <v>0.8888888955116272</v>
       </c>
       <c r="D24" t="n">
-        <v>0.008239873684942722</v>
+        <v>0.005159746389836073</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3875597715377808</v>
+        <v>0.343798816204071</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8666666746139526</v>
+        <v>0.8888888955116272</v>
       </c>
       <c r="D25" t="n">
-        <v>0.008920738473534584</v>
+        <v>0.006685230880975723</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3661619424819946</v>
+        <v>0.3433025777339935</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8666666746139526</v>
+        <v>0.8888888955116272</v>
       </c>
       <c r="D26" t="n">
-        <v>0.007711721584200859</v>
+        <v>0.004914392717182636</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3470108509063721</v>
+        <v>0.3406941592693329</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9111111164093018</v>
+        <v>0.8888888955116272</v>
       </c>
       <c r="D27" t="n">
-        <v>0.006062443368136883</v>
+        <v>0.01065967604517937</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3338219821453094</v>
+        <v>0.3401103913784027</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9111111164093018</v>
+        <v>0.8888888955116272</v>
       </c>
       <c r="D28" t="n">
-        <v>0.006704325787723064</v>
+        <v>0.00739689078181982</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3258492946624756</v>
+        <v>0.32321497797966</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9111111164093018</v>
+        <v>0.8888888955116272</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005444170907139778</v>
+        <v>0.004919377621263266</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3190996050834656</v>
+        <v>0.3057487010955811</v>
       </c>
     </row>
     <row r="30">
@@ -942,10 +942,10 @@
         <v>0.9111111164093018</v>
       </c>
       <c r="D30" t="n">
-        <v>0.005316890776157379</v>
+        <v>0.004186376929283142</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3115487694740295</v>
+        <v>0.2935648262500763</v>
       </c>
     </row>
     <row r="31">
@@ -959,10 +959,10 @@
         <v>0.9111111164093018</v>
       </c>
       <c r="D31" t="n">
-        <v>0.005792852956801653</v>
+        <v>0.002773275831714272</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3076475858688354</v>
+        <v>0.2889621257781982</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9111111164093018</v>
+        <v>0.9333333373069763</v>
       </c>
       <c r="D32" t="n">
-        <v>0.005029904190450907</v>
+        <v>0.004038716200739145</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3039984703063965</v>
+        <v>0.2829769849777222</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9111111164093018</v>
+        <v>0.9333333373069763</v>
       </c>
       <c r="D33" t="n">
-        <v>0.005685731302946806</v>
+        <v>0.006296970881521702</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3055047690868378</v>
+        <v>0.2755917906761169</v>
       </c>
     </row>
     <row r="34">
@@ -1010,10 +1010,10 @@
         <v>0.9333333373069763</v>
       </c>
       <c r="D34" t="n">
-        <v>0.006770219188183546</v>
+        <v>0.00284179812297225</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3088167905807495</v>
+        <v>0.2772301733493805</v>
       </c>
     </row>
     <row r="35">
@@ -1027,10 +1027,10 @@
         <v>0.9333333373069763</v>
       </c>
       <c r="D35" t="n">
-        <v>0.006421656347811222</v>
+        <v>0.004446972161531448</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3218224346637726</v>
+        <v>0.2821298241615295</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9111111164093018</v>
+        <v>0.9333333373069763</v>
       </c>
       <c r="D36" t="n">
-        <v>0.003917567431926727</v>
+        <v>0.001891679712571204</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3329276144504547</v>
+        <v>0.2915211617946625</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,30 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9111111164093018</v>
+        <v>0.9333333373069763</v>
       </c>
       <c r="D37" t="n">
-        <v>0.007007554639130831</v>
+        <v>0.002966730855405331</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3382514417171478</v>
+        <v>0.2961214184761047</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.9333333373069763</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.003099731635302305</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.2925739586353302</v>
       </c>
     </row>
   </sheetData>
